--- a/artfynd/A 7350-2025 artfynd.xlsx
+++ b/artfynd/A 7350-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,6 +791,267 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123083332</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bockeberga, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>371863</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6625554</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123083299</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56688</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bockeberga, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>371863</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6625554</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Skrämde upp</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7350-2025 artfynd.xlsx
+++ b/artfynd/A 7350-2025 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123083332</v>
+        <v>123083299</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>56688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,41 +806,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -896,6 +896,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>07:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skrämde upp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123083299</v>
+        <v>123083332</v>
       </c>
       <c r="B4" t="n">
-        <v>56688</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,41 +939,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1024,11 +1029,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>07:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Skrämde upp</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7350-2025 artfynd.xlsx
+++ b/artfynd/A 7350-2025 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123083299</v>
+        <v>123083332</v>
       </c>
       <c r="B3" t="n">
-        <v>56688</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,41 +806,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -896,11 +896,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>07:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Skrämde upp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123083332</v>
+        <v>123083299</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>56688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,41 +934,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1029,6 +1024,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>07:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Skrämde upp</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7350-2025 artfynd.xlsx
+++ b/artfynd/A 7350-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122923581</v>
       </c>
       <c r="B2" t="n">
-        <v>57629</v>
+        <v>57632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123083299</v>
+        <v>123083332</v>
       </c>
       <c r="B3" t="n">
-        <v>56688</v>
+        <v>57634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,41 +806,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -896,11 +896,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>07:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Skrämde upp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123083332</v>
+        <v>123083299</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>56691</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,41 +934,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1029,6 +1024,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>07:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Skrämde upp</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7350-2025 artfynd.xlsx
+++ b/artfynd/A 7350-2025 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123083332</v>
+        <v>123083299</v>
       </c>
       <c r="B3" t="n">
-        <v>57634</v>
+        <v>56691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,41 +806,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -896,6 +896,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>07:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skrämde upp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123083299</v>
+        <v>123083332</v>
       </c>
       <c r="B4" t="n">
-        <v>56691</v>
+        <v>57634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,41 +939,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1024,11 +1029,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>07:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Skrämde upp</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7350-2025 artfynd.xlsx
+++ b/artfynd/A 7350-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122923581</v>
       </c>
       <c r="B2" t="n">
-        <v>57632</v>
+        <v>57638</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>123083299</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>123083332</v>
       </c>
       <c r="B4" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 7350-2025 artfynd.xlsx
+++ b/artfynd/A 7350-2025 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123083299</v>
+        <v>123083332</v>
       </c>
       <c r="B3" t="n">
-        <v>56697</v>
+        <v>57643</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,41 +806,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -896,11 +896,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>07:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Skrämde upp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123083332</v>
+        <v>123083299</v>
       </c>
       <c r="B4" t="n">
-        <v>57640</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,41 +934,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1029,6 +1024,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>07:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Skrämde upp</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7350-2025 artfynd.xlsx
+++ b/artfynd/A 7350-2025 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123083332</v>
+        <v>123083299</v>
       </c>
       <c r="B3" t="n">
-        <v>57643</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,41 +806,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -896,6 +896,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>07:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skrämde upp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123083299</v>
+        <v>123083332</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,41 +939,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1024,11 +1029,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>07:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Skrämde upp</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7350-2025 artfynd.xlsx
+++ b/artfynd/A 7350-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,40 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122923581</v>
+        <v>122904454</v>
       </c>
       <c r="B2" t="n">
-        <v>57638</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>371787</v>
+        <v>371929</v>
       </c>
       <c r="R2" t="n">
-        <v>6625507</v>
+        <v>6625542</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,17 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Meståg</t>
+          <t>16 tjädertallar med rikliga spillningshögar inunder träden</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123083299</v>
+        <v>122923448</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,7 +815,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -850,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>371863</v>
+        <v>371845</v>
       </c>
       <c r="R3" t="n">
-        <v>6625554</v>
+        <v>6625505</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,27 +866,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Skrämde upp</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,53 +898,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123083332</v>
+        <v>123083299</v>
       </c>
       <c r="B4" t="n">
-        <v>57644</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1031,6 +997,11 @@
           <t>07:30</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Skrämde upp</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1052,6 +1023,243 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122923581</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bockeberga, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>371787</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6625507</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Meståg</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123083332</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bockeberga, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>371863</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6625554</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
